--- a/Results/tables/Species_Density_and_Model_Coefficients_Summary.xlsx
+++ b/Results/tables/Species_Density_and_Model_Coefficients_Summary.xlsx
@@ -450,43 +450,43 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.4257728107101973</v>
+        <v>0.4603806022619116</v>
       </c>
       <c r="D2">
-        <v>0.3890824788212293</v>
+        <v>0.441181532448877</v>
       </c>
       <c r="E2">
-        <v>0.009120747697606083</v>
+        <v>0.008538309347595906</v>
       </c>
       <c r="F2">
-        <v>0.3512151203667369</v>
+        <v>0.3804858177285327</v>
       </c>
       <c r="G2">
-        <v>0.1852404341395633</v>
+        <v>0.2032203739117764</v>
       </c>
       <c r="H2">
-        <v>0.2031780842929501</v>
+        <v>0.222154777553159</v>
       </c>
       <c r="I2">
-        <v>0.2262623627346061</v>
+        <v>0.2458004195062564</v>
       </c>
       <c r="J2">
-        <v>0.2743791581081529</v>
+        <v>0.2984205969913146</v>
       </c>
       <c r="K2">
-        <v>0.3512151203667369</v>
+        <v>0.3804858177285327</v>
       </c>
       <c r="L2">
-        <v>0.469354519283368</v>
+        <v>0.5063502950510423</v>
       </c>
       <c r="M2">
-        <v>0.660481984355881</v>
+        <v>0.7050035927231841</v>
       </c>
       <c r="N2">
-        <v>0.8466952444864765</v>
+        <v>0.9063924376588084</v>
       </c>
       <c r="O2">
-        <v>1.045551655597013</v>
+        <v>1.128763330386232</v>
       </c>
     </row>
     <row r="3">
@@ -501,43 +501,43 @@
         </is>
       </c>
       <c r="C3">
-        <v>1282.001933048404</v>
+        <v>1386.205993410616</v>
       </c>
       <c r="D3">
-        <v>1171.527343730721</v>
+        <v>1328.397594203569</v>
       </c>
       <c r="E3">
-        <v>27.46257131749193</v>
+        <v>25.70884944561126</v>
       </c>
       <c r="F3">
-        <v>1057.508727424245</v>
+        <v>1145.642797180612</v>
       </c>
       <c r="G3">
-        <v>557.7589471942249</v>
+        <v>611.8965458483589</v>
       </c>
       <c r="H3">
-        <v>611.769211806073</v>
+        <v>668.9080352125616</v>
       </c>
       <c r="I3">
-        <v>681.2759741938989</v>
+        <v>740.105063133338</v>
       </c>
       <c r="J3">
-        <v>826.1556450636485</v>
+        <v>898.5444175408481</v>
       </c>
       <c r="K3">
-        <v>1057.508727424245</v>
+        <v>1145.642797180612</v>
       </c>
       <c r="L3">
-        <v>1413.226457562221</v>
+        <v>1524.620738398688</v>
       </c>
       <c r="M3">
-        <v>1988.711254895557</v>
+        <v>2122.765817689507</v>
       </c>
       <c r="N3">
-        <v>2549.399381148781</v>
+        <v>2729.147629790672</v>
       </c>
       <c r="O3">
-        <v>3148.156035002605</v>
+        <v>3398.706387792945</v>
       </c>
     </row>
     <row r="4">
@@ -654,43 +654,43 @@
         </is>
       </c>
       <c r="C6">
-        <v>2.667547219172076</v>
+        <v>1.949751372361247</v>
       </c>
       <c r="D6">
-        <v>0.5644243107926143</v>
+        <v>0.4127238525622873</v>
       </c>
       <c r="E6">
-        <v>0.02409490047095576</v>
+        <v>0.01758881480212163</v>
       </c>
       <c r="F6">
-        <v>2.582508906328016</v>
+        <v>1.887606717040101</v>
       </c>
       <c r="G6">
-        <v>1.834036083832236</v>
+        <v>1.342110907622697</v>
       </c>
       <c r="H6">
-        <v>1.936334273916042</v>
+        <v>1.416944325199236</v>
       </c>
       <c r="I6">
-        <v>2.061528317048691</v>
+        <v>1.507020869044737</v>
       </c>
       <c r="J6">
-        <v>2.280821560804984</v>
+        <v>1.667497653454624</v>
       </c>
       <c r="K6">
-        <v>2.582508906328016</v>
+        <v>1.887606717040101</v>
       </c>
       <c r="L6">
-        <v>2.943254499642864</v>
+        <v>2.152114263272574</v>
       </c>
       <c r="M6">
-        <v>3.380706212271892</v>
+        <v>2.471546365471177</v>
       </c>
       <c r="N6">
-        <v>3.720332973452596</v>
+        <v>2.71600557376548</v>
       </c>
       <c r="O6">
-        <v>3.993781293326881</v>
+        <v>2.928082131272063</v>
       </c>
     </row>
     <row r="7">
@@ -705,43 +705,43 @@
         </is>
       </c>
       <c r="C7">
-        <v>8031.984676927121</v>
+        <v>5870.701382179715</v>
       </c>
       <c r="D7">
-        <v>1699.481599796562</v>
+        <v>1242.711520065047</v>
       </c>
       <c r="E7">
-        <v>72.54974531804775</v>
+        <v>52.95992136918829</v>
       </c>
       <c r="F7">
-        <v>7775.934316953658</v>
+        <v>5683.583825007742</v>
       </c>
       <c r="G7">
-        <v>5522.282648418864</v>
+        <v>4041.095942851939</v>
       </c>
       <c r="H7">
-        <v>5830.302498761203</v>
+        <v>4266.419363174899</v>
       </c>
       <c r="I7">
-        <v>6207.26176263361</v>
+        <v>4537.639836693703</v>
       </c>
       <c r="J7">
-        <v>6867.553719583807</v>
+        <v>5020.835434551874</v>
       </c>
       <c r="K7">
-        <v>7775.934316953658</v>
+        <v>5683.583825007742</v>
       </c>
       <c r="L7">
-        <v>8862.139298424663</v>
+        <v>6480.01604671372</v>
       </c>
       <c r="M7">
-        <v>10179.30640515067</v>
+        <v>7441.826106433715</v>
       </c>
       <c r="N7">
-        <v>11201.92258306577</v>
+        <v>8177.892782607859</v>
       </c>
       <c r="O7">
-        <v>12025.27547420724</v>
+        <v>8816.455297260183</v>
       </c>
     </row>
     <row r="8">
@@ -858,43 +858,43 @@
         </is>
       </c>
       <c r="C10">
-        <v>1.36603810430096</v>
+        <v>0.9964500081095705</v>
       </c>
       <c r="D10">
-        <v>3.119426065570579</v>
+        <v>2.297736761537587</v>
       </c>
       <c r="E10">
-        <v>0.04643061864689123</v>
+        <v>0.03411180370843789</v>
       </c>
       <c r="F10">
-        <v>0.9922567757260041</v>
+        <v>0.725056763629079</v>
       </c>
       <c r="G10">
-        <v>0.4669698727680902</v>
+        <v>0.3418581011347069</v>
       </c>
       <c r="H10">
-        <v>0.5193689400835841</v>
+        <v>0.37898593462665</v>
       </c>
       <c r="I10">
-        <v>0.5961656638898478</v>
+        <v>0.436400012384547</v>
       </c>
       <c r="J10">
-        <v>0.7494084158361531</v>
+        <v>0.5462346812144563</v>
       </c>
       <c r="K10">
-        <v>0.9922567757260041</v>
+        <v>0.725056763629079</v>
       </c>
       <c r="L10">
-        <v>1.406892062145011</v>
+        <v>1.02497131686808</v>
       </c>
       <c r="M10">
-        <v>2.133194124481725</v>
+        <v>1.54681650932889</v>
       </c>
       <c r="N10">
-        <v>2.984501091419826</v>
+        <v>2.163675681568962</v>
       </c>
       <c r="O10">
-        <v>4.300251767286466</v>
+        <v>3.117009035720792</v>
       </c>
     </row>
     <row r="11">
@@ -909,43 +909,43 @@
         </is>
       </c>
       <c r="C11">
-        <v>4113.14073205019</v>
+        <v>3000.310974417917</v>
       </c>
       <c r="D11">
-        <v>9392.591883433011</v>
+        <v>6918.485388989674</v>
       </c>
       <c r="E11">
-        <v>139.8025927457896</v>
+        <v>102.7106409661066</v>
       </c>
       <c r="F11">
-        <v>2987.685151710998</v>
+        <v>2183.145915287157</v>
       </c>
       <c r="G11">
-        <v>1406.046286904719</v>
+        <v>1029.334742516602</v>
       </c>
       <c r="H11">
-        <v>1563.819878591672</v>
+        <v>1141.126649160843</v>
       </c>
       <c r="I11">
-        <v>1795.054813972332</v>
+        <v>1314.000437289871</v>
       </c>
       <c r="J11">
-        <v>2256.468740082657</v>
+        <v>1644.712625136728</v>
       </c>
       <c r="K11">
-        <v>2987.685151710998</v>
+        <v>2183.145915287157</v>
       </c>
       <c r="L11">
-        <v>4236.151999118628</v>
+        <v>3086.188635089789</v>
       </c>
       <c r="M11">
-        <v>6423.047508814474</v>
+        <v>4657.464509589288</v>
       </c>
       <c r="N11">
-        <v>8986.332786265097</v>
+        <v>6514.827477204146</v>
       </c>
       <c r="O11">
-        <v>12948.05807129955</v>
+        <v>9385.314206555306</v>
       </c>
     </row>
     <row r="12">
@@ -1062,43 +1062,43 @@
         </is>
       </c>
       <c r="C14">
-        <v>4.023831503303585</v>
+        <v>2.692335028946356</v>
       </c>
       <c r="D14">
-        <v>0.3667505261533778</v>
+        <v>0.2449943049434862</v>
       </c>
       <c r="E14">
-        <v>0.005459327981347391</v>
+        <v>0.00363845930898833</v>
       </c>
       <c r="F14">
-        <v>4.006972167688392</v>
+        <v>2.679136548049308</v>
       </c>
       <c r="G14">
-        <v>3.367596463325184</v>
+        <v>2.251480683976385</v>
       </c>
       <c r="H14">
-        <v>3.452715379671594</v>
+        <v>2.310105325724013</v>
       </c>
       <c r="I14">
-        <v>3.570258181016992</v>
+        <v>2.387749864253066</v>
       </c>
       <c r="J14">
-        <v>3.76748535400509</v>
+        <v>2.521127440790953</v>
       </c>
       <c r="K14">
-        <v>4.006972167688392</v>
+        <v>2.679136548049308</v>
       </c>
       <c r="L14">
-        <v>4.258481148568404</v>
+        <v>2.848521373421197</v>
       </c>
       <c r="M14">
-        <v>4.496672000136937</v>
+        <v>3.008756696550765</v>
       </c>
       <c r="N14">
-        <v>4.657194051919454</v>
+        <v>3.121132070102963</v>
       </c>
       <c r="O14">
-        <v>4.79213236337714</v>
+        <v>3.204951641079247</v>
       </c>
     </row>
     <row r="15">
@@ -1113,43 +1113,43 @@
         </is>
       </c>
       <c r="C15">
-        <v>12115.7566564471</v>
+        <v>8106.620772157479</v>
       </c>
       <c r="D15">
-        <v>1104.285834247821</v>
+        <v>737.6778521848369</v>
       </c>
       <c r="E15">
-        <v>16.43803655183701</v>
+        <v>10.95540097936387</v>
       </c>
       <c r="F15">
-        <v>12064.99319690975</v>
+        <v>8066.880146176466</v>
       </c>
       <c r="G15">
-        <v>10139.83295107213</v>
+        <v>6779.208339452894</v>
       </c>
       <c r="H15">
-        <v>10396.12600819117</v>
+        <v>6955.727135755003</v>
       </c>
       <c r="I15">
-        <v>10750.04738304217</v>
+        <v>7189.514841265982</v>
       </c>
       <c r="J15">
-        <v>11343.89840090933</v>
+        <v>7591.114724221561</v>
       </c>
       <c r="K15">
-        <v>12064.99319690975</v>
+        <v>8066.880146176466</v>
       </c>
       <c r="L15">
-        <v>12822.28673833946</v>
+        <v>8576.897855371226</v>
       </c>
       <c r="M15">
-        <v>13539.47939241232</v>
+        <v>9059.366413314352</v>
       </c>
       <c r="N15">
-        <v>14022.81129032948</v>
+        <v>9397.728663080023</v>
       </c>
       <c r="O15">
-        <v>14429.11054612857</v>
+        <v>9650.109391289612</v>
       </c>
     </row>
     <row r="16">
@@ -1266,43 +1266,43 @@
         </is>
       </c>
       <c r="C18">
-        <v>1.050787975655599</v>
+        <v>1.27603599754124</v>
       </c>
       <c r="D18">
-        <v>0.4162596799929882</v>
+        <v>0.5040801664148741</v>
       </c>
       <c r="E18">
-        <v>0.00928494438570766</v>
+        <v>0.01106139884632885</v>
       </c>
       <c r="F18">
-        <v>0.9642837789846578</v>
+        <v>1.169662246861612</v>
       </c>
       <c r="G18">
-        <v>0.5541226059000345</v>
+        <v>0.6726984635600087</v>
       </c>
       <c r="H18">
-        <v>0.5996049456178824</v>
+        <v>0.7291819716314556</v>
       </c>
       <c r="I18">
-        <v>0.6636677092121471</v>
+        <v>0.8071553382512031</v>
       </c>
       <c r="J18">
-        <v>0.7913403684330155</v>
+        <v>0.9581738734904842</v>
       </c>
       <c r="K18">
-        <v>0.9642837789846578</v>
+        <v>1.169662246861612</v>
       </c>
       <c r="L18">
-        <v>1.199544970800787</v>
+        <v>1.460583661714534</v>
       </c>
       <c r="M18">
-        <v>1.513553394935428</v>
+        <v>1.845026208077151</v>
       </c>
       <c r="N18">
-        <v>1.77079780008639</v>
+        <v>2.144868246451618</v>
       </c>
       <c r="O18">
-        <v>2.112859729751993</v>
+        <v>2.552674522900654</v>
       </c>
     </row>
     <row r="19">
@@ -1317,43 +1317,43 @@
         </is>
       </c>
       <c r="C19">
-        <v>3163.922594699008</v>
+        <v>3842.144388596672</v>
       </c>
       <c r="D19">
-        <v>1253.357896458888</v>
+        <v>1517.785381075186</v>
       </c>
       <c r="E19">
-        <v>27.9569675453658</v>
+        <v>33.30587192629623</v>
       </c>
       <c r="F19">
-        <v>2903.458458522805</v>
+        <v>3521.853025300315</v>
       </c>
       <c r="G19">
-        <v>1668.463166365003</v>
+        <v>2025.495073779186</v>
       </c>
       <c r="H19">
-        <v>1805.410491255444</v>
+        <v>2195.566916582313</v>
       </c>
       <c r="I19">
-        <v>1998.303472437775</v>
+        <v>2430.344723474373</v>
       </c>
       <c r="J19">
-        <v>2382.72584935181</v>
+        <v>2885.061533079848</v>
       </c>
       <c r="K19">
-        <v>2903.458458522805</v>
+        <v>3521.853025300315</v>
       </c>
       <c r="L19">
-        <v>3611.829907081172</v>
+        <v>4397.817405422461</v>
       </c>
       <c r="M19">
-        <v>4557.309272150575</v>
+        <v>5555.373912520302</v>
       </c>
       <c r="N19">
-        <v>5331.872176060122</v>
+        <v>6458.198290065822</v>
       </c>
       <c r="O19">
-        <v>6361.82064628325</v>
+        <v>7686.102988453868</v>
       </c>
     </row>
     <row r="20">
